--- a/docs/downloads/27082026Tduh Developer Project Sales Status 13.xlsx
+++ b/docs/downloads/27082026Tduh Developer Project Sales Status 13.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:BC18"/>
+  <dimension ref="A2:BF18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -543,6 +543,9 @@
     <col width="9" customWidth="1" min="53" max="53"/>
     <col width="9" customWidth="1" min="54" max="54"/>
     <col width="9" customWidth="1" min="55" max="55"/>
+    <col width="9" customWidth="1" min="56" max="56"/>
+    <col width="9" customWidth="1" min="57" max="57"/>
+    <col width="9" customWidth="1" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -606,8 +609,11 @@
       <c r="AX3" s="3" t="n">
         <v>46248</v>
       </c>
-      <c r="BA3" s="4" t="n">
+      <c r="BA3" s="3" t="n">
         <v>46255</v>
+      </c>
+      <c r="BD3" s="4" t="n">
+        <v>46262</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -873,17 +879,32 @@
           <t>%</t>
         </is>
       </c>
-      <c r="BA4" s="6" t="inlineStr">
+      <c r="BA4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW SALES </t>
         </is>
       </c>
-      <c r="BB4" s="6" t="inlineStr">
+      <c r="BB4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="BC4" s="6" t="inlineStr">
+      <c r="BC4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BD4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW SALES </t>
+        </is>
+      </c>
+      <c r="BE4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BF4" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -963,15 +984,26 @@
         <f>AY5/$E$5</f>
         <v/>
       </c>
-      <c r="BA5" s="11">
+      <c r="BA5" s="9">
         <f>BB5-AY5</f>
         <v/>
       </c>
-      <c r="BB5" s="11" t="n">
+      <c r="BB5" s="9" t="n">
         <v>183</v>
       </c>
-      <c r="BC5" s="12">
+      <c r="BC5" s="10">
         <f>BB5/$E$5</f>
+        <v/>
+      </c>
+      <c r="BD5" s="11">
+        <f>BE5-BB5</f>
+        <v/>
+      </c>
+      <c r="BE5" s="11" t="n">
+        <v>186</v>
+      </c>
+      <c r="BF5" s="12">
+        <f>BE5/$E$5</f>
         <v/>
       </c>
     </row>
@@ -1169,15 +1201,26 @@
         <f>AY6/$E$6</f>
         <v/>
       </c>
-      <c r="BA6" s="11">
+      <c r="BA6" s="9">
         <f>BB6-AY6</f>
         <v/>
       </c>
-      <c r="BB6" s="11" t="n">
+      <c r="BB6" s="9" t="n">
         <v>344</v>
       </c>
-      <c r="BC6" s="12">
+      <c r="BC6" s="10">
         <f>BB6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BD6" s="11">
+        <f>BE6-BB6</f>
+        <v/>
+      </c>
+      <c r="BE6" s="11" t="n">
+        <v>353</v>
+      </c>
+      <c r="BF6" s="12">
+        <f>BE6/$E$6</f>
         <v/>
       </c>
     </row>
@@ -1376,15 +1419,26 @@
         <f>AY7/$E$7</f>
         <v/>
       </c>
-      <c r="BA7" s="11">
+      <c r="BA7" s="9">
         <f>BB7-AY7</f>
         <v/>
       </c>
-      <c r="BB7" s="11" t="n">
+      <c r="BB7" s="9" t="n">
         <v>123</v>
       </c>
-      <c r="BC7" s="12">
+      <c r="BC7" s="10">
         <f>BB7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BD7" s="11">
+        <f>BE7-BB7</f>
+        <v/>
+      </c>
+      <c r="BE7" s="11" t="n">
+        <v>127</v>
+      </c>
+      <c r="BF7" s="12">
+        <f>BE7/$E$7</f>
         <v/>
       </c>
     </row>
@@ -1582,15 +1636,26 @@
         <f>AY8/$E$8</f>
         <v/>
       </c>
-      <c r="BA8" s="11">
+      <c r="BA8" s="9">
         <f>BB8-AY8</f>
         <v/>
       </c>
-      <c r="BB8" s="11" t="n">
+      <c r="BB8" s="9" t="n">
         <v>1003</v>
       </c>
-      <c r="BC8" s="12">
+      <c r="BC8" s="10">
         <f>BB8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BD8" s="11">
+        <f>BE8-BB8</f>
+        <v/>
+      </c>
+      <c r="BE8" s="11" t="n">
+        <v>1009</v>
+      </c>
+      <c r="BF8" s="12">
+        <f>BE8/$E$8</f>
         <v/>
       </c>
     </row>
@@ -1789,15 +1854,26 @@
         <f>AY9/$E$9</f>
         <v/>
       </c>
-      <c r="BA9" s="11">
+      <c r="BA9" s="9">
         <f>BB9-AY9</f>
         <v/>
       </c>
-      <c r="BB9" s="11" t="n">
+      <c r="BB9" s="9" t="n">
         <v>1125</v>
       </c>
-      <c r="BC9" s="12">
+      <c r="BC9" s="10">
         <f>BB9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BD9" s="11">
+        <f>BE9-BB9</f>
+        <v/>
+      </c>
+      <c r="BE9" s="11" t="n">
+        <v>1126</v>
+      </c>
+      <c r="BF9" s="12">
+        <f>BE9/$E$9</f>
         <v/>
       </c>
     </row>
@@ -1996,15 +2072,26 @@
         <f>AY10/$E$10</f>
         <v/>
       </c>
-      <c r="BA10" s="11">
+      <c r="BA10" s="9">
         <f>BB10-AY10</f>
         <v/>
       </c>
-      <c r="BB10" s="11" t="n">
+      <c r="BB10" s="9" t="n">
         <v>509</v>
       </c>
-      <c r="BC10" s="12">
+      <c r="BC10" s="10">
         <f>BB10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BD10" s="11">
+        <f>BE10-BB10</f>
+        <v/>
+      </c>
+      <c r="BE10" s="11" t="n">
+        <v>517</v>
+      </c>
+      <c r="BF10" s="12">
+        <f>BE10/$E$10</f>
         <v/>
       </c>
     </row>
@@ -2202,15 +2289,26 @@
         <f>AY11/$E$11</f>
         <v/>
       </c>
-      <c r="BA11" s="11">
+      <c r="BA11" s="9">
         <f>BB11-AY11</f>
         <v/>
       </c>
-      <c r="BB11" s="11" t="n">
+      <c r="BB11" s="9" t="n">
         <v>467</v>
       </c>
-      <c r="BC11" s="12">
+      <c r="BC11" s="10">
         <f>BB11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BD11" s="11">
+        <f>BE11-BB11</f>
+        <v/>
+      </c>
+      <c r="BE11" s="11" t="n">
+        <v>467</v>
+      </c>
+      <c r="BF11" s="12">
+        <f>BE11/$E$11</f>
         <v/>
       </c>
     </row>
@@ -2408,15 +2506,26 @@
         <f>AY12/$E$12</f>
         <v/>
       </c>
-      <c r="BA12" s="11">
+      <c r="BA12" s="9">
         <f>BB12-AY12</f>
         <v/>
       </c>
-      <c r="BB12" s="11" t="n">
+      <c r="BB12" s="9" t="n">
         <v>236</v>
       </c>
-      <c r="BC12" s="12">
+      <c r="BC12" s="10">
         <f>BB12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BD12" s="11">
+        <f>BE12-BB12</f>
+        <v/>
+      </c>
+      <c r="BE12" s="11" t="n">
+        <v>237</v>
+      </c>
+      <c r="BF12" s="12">
+        <f>BE12/$E$12</f>
         <v/>
       </c>
     </row>
@@ -2615,15 +2724,26 @@
         <f>AY13/$E$13</f>
         <v/>
       </c>
-      <c r="BA13" s="11">
+      <c r="BA13" s="9">
         <f>BB13-AY13</f>
         <v/>
       </c>
-      <c r="BB13" s="11" t="n">
+      <c r="BB13" s="9" t="n">
         <v>626</v>
       </c>
-      <c r="BC13" s="12">
+      <c r="BC13" s="10">
         <f>BB13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BD13" s="11">
+        <f>BE13-BB13</f>
+        <v/>
+      </c>
+      <c r="BE13" s="11" t="n">
+        <v>642</v>
+      </c>
+      <c r="BF13" s="12">
+        <f>BE13/$E$13</f>
         <v/>
       </c>
     </row>
@@ -2821,15 +2941,26 @@
         <f>AY14/$E$14</f>
         <v/>
       </c>
-      <c r="BA14" s="11">
+      <c r="BA14" s="9">
         <f>BB14-AY14</f>
         <v/>
       </c>
-      <c r="BB14" s="11" t="n">
+      <c r="BB14" s="9" t="n">
         <v>1151</v>
       </c>
-      <c r="BC14" s="12">
+      <c r="BC14" s="10">
         <f>BB14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BD14" s="11">
+        <f>BE14-BB14</f>
+        <v/>
+      </c>
+      <c r="BE14" s="11" t="n">
+        <v>1155</v>
+      </c>
+      <c r="BF14" s="12">
+        <f>BE14/$E$14</f>
         <v/>
       </c>
     </row>
@@ -3027,15 +3158,26 @@
         <f>AY15/$E$15</f>
         <v/>
       </c>
-      <c r="BA15" s="11">
+      <c r="BA15" s="9">
         <f>BB15-AY15</f>
         <v/>
       </c>
-      <c r="BB15" s="11" t="n">
+      <c r="BB15" s="9" t="n">
         <v>127</v>
       </c>
-      <c r="BC15" s="12">
+      <c r="BC15" s="10">
         <f>BB15/$E$15</f>
+        <v/>
+      </c>
+      <c r="BD15" s="11">
+        <f>BE15-BB15</f>
+        <v/>
+      </c>
+      <c r="BE15" s="11" t="n">
+        <v>132</v>
+      </c>
+      <c r="BF15" s="12">
+        <f>BE15/$E$15</f>
         <v/>
       </c>
     </row>
@@ -3169,15 +3311,26 @@
         <f>AY16/$E$16</f>
         <v/>
       </c>
-      <c r="BA16" s="11">
+      <c r="BA16" s="9">
         <f>BB16-AY16</f>
         <v/>
       </c>
-      <c r="BB16" s="11" t="n">
+      <c r="BB16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BC16" s="12">
+      <c r="BC16" s="10">
         <f>BB16/$E$16</f>
+        <v/>
+      </c>
+      <c r="BD16" s="11">
+        <f>BE16-BB16</f>
+        <v/>
+      </c>
+      <c r="BE16" s="11" t="n">
+        <v>659</v>
+      </c>
+      <c r="BF16" s="12">
+        <f>BE16/$E$16</f>
         <v/>
       </c>
     </row>
@@ -3246,9 +3399,12 @@
       <c r="AX17" s="9" t="n"/>
       <c r="AY17" s="9" t="n"/>
       <c r="AZ17" s="10" t="n"/>
-      <c r="BA17" s="11" t="n"/>
-      <c r="BB17" s="11" t="n"/>
-      <c r="BC17" s="12" t="n"/>
+      <c r="BA17" s="9" t="n"/>
+      <c r="BB17" s="9" t="n"/>
+      <c r="BC17" s="10" t="n"/>
+      <c r="BD17" s="11" t="n"/>
+      <c r="BE17" s="11" t="n"/>
+      <c r="BF17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -3324,20 +3480,31 @@
         <f>AY18/$E$18</f>
         <v/>
       </c>
-      <c r="BA18" s="11">
+      <c r="BA18" s="9">
         <f>BB18-AY18</f>
         <v/>
       </c>
-      <c r="BB18" s="11" t="n">
+      <c r="BB18" s="9" t="n">
         <v>191</v>
       </c>
-      <c r="BC18" s="12">
+      <c r="BC18" s="10">
         <f>BB18/$E$18</f>
+        <v/>
+      </c>
+      <c r="BD18" s="11">
+        <f>BE18-BB18</f>
+        <v/>
+      </c>
+      <c r="BE18" s="11" t="n">
+        <v>246</v>
+      </c>
+      <c r="BF18" s="12">
+        <f>BE18/$E$18</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="AU3:AW3"/>
     <mergeCell ref="BA3:BC3"/>
@@ -3354,6 +3521,7 @@
     <mergeCell ref="AL3:AN3"/>
     <mergeCell ref="AO3:AQ3"/>
     <mergeCell ref="N3:P3"/>
+    <mergeCell ref="BD3:BF3"/>
     <mergeCell ref="Q3:S3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
